--- a/pracovný čas _ Dispečeri.xlsx
+++ b/pracovný čas _ Dispečeri.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{F1670604-6CA9-4FF5-B522-8001B27FFD27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27690" yWindow="30" windowWidth="19545" windowHeight="15600" xr2:uid="{373562B3-80CF-4473-92E0-10396789CD95}"/>
+    <workbookView xWindow="-20070" yWindow="0" windowWidth="14475" windowHeight="15600" xr2:uid="{373562B3-80CF-4473-92E0-10396789CD95}"/>
   </bookViews>
   <sheets>
     <sheet name="Hárok1" sheetId="1" r:id="rId1"/>
@@ -75,8 +75,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="8" formatCode="#,##0.00\ &quot;€&quot;;[Red]\-#,##0.00\ &quot;€&quot;"/>
-    <numFmt numFmtId="167" formatCode="#,##0.00\ &quot;€&quot;"/>
-    <numFmt numFmtId="168" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;€&quot;"/>
+    <numFmt numFmtId="165" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -203,51 +203,51 @@
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="8" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="8" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="8" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -569,122 +569,122 @@
     <col min="3" max="3" width="13.42578125" customWidth="1"/>
     <col min="4" max="4" width="11.140625" customWidth="1"/>
     <col min="5" max="5" width="21.28515625" customWidth="1"/>
-    <col min="6" max="6" width="15.85546875" style="11" customWidth="1"/>
+    <col min="6" max="6" width="15.85546875" style="7" customWidth="1"/>
     <col min="7" max="7" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="3:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="11" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="3:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="3"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="3"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="12"/>
     </row>
     <row r="5" spans="3:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="2">
         <v>40.6</v>
       </c>
-      <c r="E5" s="10">
+      <c r="E5" s="6">
         <f>D5*G5*24</f>
         <v>81.199999999999989</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="F5" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="8">
+      <c r="G5" s="4">
         <f>MOD(TIMEVALUE(TRIM(MID(F5,FIND("-",F5)+1,99)))-TIMEVALUE(TRIM(LEFT(F5,FIND("-",F5)-1))),1)</f>
         <v>8.3333333333333315E-2</v>
       </c>
     </row>
     <row r="6" spans="3:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="2">
         <v>40.6</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="6">
         <f t="shared" ref="E6:E8" si="0">D6*G6*24</f>
         <v>135.33333333333334</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="F6" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="4">
         <f t="shared" ref="G6:G8" si="1">MOD(TIMEVALUE(TRIM(MID(F6,FIND("-",F6)+1,99)))-TIMEVALUE(TRIM(LEFT(F6,FIND("-",F6)-1))),1)</f>
         <v>0.1388888888888889</v>
       </c>
     </row>
     <row r="7" spans="3:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="3">
         <v>40.6</v>
       </c>
-      <c r="E7" s="10">
+      <c r="E7" s="6">
         <f t="shared" si="0"/>
         <v>16.916666666666664</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="F7" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7" s="4">
         <f t="shared" si="1"/>
         <v>1.7361111111111105E-2</v>
       </c>
     </row>
     <row r="8" spans="3:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="2">
         <v>40.6</v>
       </c>
-      <c r="E8" s="10">
+      <c r="E8" s="6">
         <f t="shared" si="0"/>
         <v>78.493333333333325</v>
       </c>
-      <c r="F8" s="14" t="s">
+      <c r="F8" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G8" s="4">
         <f t="shared" si="1"/>
         <v>8.0555555555555547E-2</v>
       </c>
     </row>
     <row r="11" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="E11" s="9"/>
+      <c r="E11" s="5"/>
     </row>
     <row r="13" spans="3:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="14" spans="3:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E14" s="16" t="s">
+      <c r="E14" s="10" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="15" spans="3:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E15" s="15">
+      <c r="E15" s="9">
         <f>SUM(E5:E8)</f>
         <v>311.94333333333333</v>
       </c>
